--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.4068561385749</v>
+        <v>7.053614122518422</v>
       </c>
       <c r="D2" t="n">
-        <v>43.35527946710793</v>
+        <v>7.045232913405039</v>
       </c>
       <c r="E2" t="n">
-        <v>12.62548052830468</v>
+        <v>2.051640585849511</v>
       </c>
       <c r="F2" t="n">
-        <v>12.58098346174265</v>
+        <v>2.04440981253318</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.29815254258901</v>
+        <v>7.685949788170714</v>
       </c>
       <c r="D3" t="n">
-        <v>47.32804111542031</v>
+        <v>7.690806681255801</v>
       </c>
       <c r="E3" t="n">
-        <v>12.62548052830468</v>
+        <v>2.051640585849511</v>
       </c>
       <c r="F3" t="n">
-        <v>12.58098346174265</v>
+        <v>2.04440981253318</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.37367520418022</v>
+        <v>5.910722220679285</v>
       </c>
       <c r="D4" t="n">
-        <v>36.17304209064369</v>
+        <v>5.8781193397296</v>
       </c>
       <c r="E4" t="n">
-        <v>12.62548052830468</v>
+        <v>2.051640585849511</v>
       </c>
       <c r="F4" t="n">
-        <v>12.58098346174265</v>
+        <v>2.04440981253318</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42.59960764313061</v>
+        <v>6.922436242008724</v>
       </c>
       <c r="D5" t="n">
-        <v>42.71041399967348</v>
+        <v>6.940442274946942</v>
       </c>
       <c r="E5" t="n">
-        <v>12.62548052830468</v>
+        <v>2.051640585849511</v>
       </c>
       <c r="F5" t="n">
-        <v>12.58098346174265</v>
+        <v>2.04440981253318</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.0679047439525</v>
+        <v>3.261034520892282</v>
       </c>
       <c r="D6" t="n">
-        <v>19.97436457504284</v>
+        <v>3.245834243444461</v>
       </c>
       <c r="E6" t="n">
-        <v>12.62548052830468</v>
+        <v>2.051640585849511</v>
       </c>
       <c r="F6" t="n">
-        <v>12.58098346174265</v>
+        <v>2.04440981253318</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>41.61761589391023</v>
+        <v>6.762862582760413</v>
       </c>
       <c r="D7" t="n">
-        <v>41.76582039794459</v>
+        <v>6.786945814665997</v>
       </c>
       <c r="E7" t="n">
-        <v>12.62548052830468</v>
+        <v>2.051640585849511</v>
       </c>
       <c r="F7" t="n">
-        <v>12.58098346174265</v>
+        <v>2.04440981253318</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.20286297239329</v>
+        <v>4.90796523301391</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79410117165404</v>
+        <v>4.841541440393781</v>
       </c>
       <c r="E8" t="n">
-        <v>12.62548052830468</v>
+        <v>2.051640585849511</v>
       </c>
       <c r="F8" t="n">
-        <v>12.58098346174265</v>
+        <v>2.04440981253318</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>19.8282055901176</v>
+        <v>3.222083408394111</v>
       </c>
       <c r="D9" t="n">
-        <v>19.42249041803831</v>
+        <v>3.156154692931226</v>
       </c>
       <c r="E9" t="n">
-        <v>12.62548052830468</v>
+        <v>2.051640585849511</v>
       </c>
       <c r="F9" t="n">
-        <v>12.58098346174265</v>
+        <v>2.04440981253318</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>40.39672544930737</v>
+        <v>6.564467885512448</v>
       </c>
       <c r="D10" t="n">
-        <v>40.213906905288</v>
+        <v>6.5347598721093</v>
       </c>
       <c r="E10" t="n">
-        <v>12.62548052830468</v>
+        <v>2.051640585849511</v>
       </c>
       <c r="F10" t="n">
-        <v>12.58098346174265</v>
+        <v>2.04440981253318</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>12.20942966899854</v>
+        <v>1.984032321212263</v>
       </c>
       <c r="D11" t="n">
-        <v>12.42082848131276</v>
+        <v>2.018384628213323</v>
       </c>
       <c r="E11" t="n">
-        <v>12.62548052830468</v>
+        <v>2.051640585849511</v>
       </c>
       <c r="F11" t="n">
-        <v>12.58098346174265</v>
+        <v>2.04440981253318</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>36.95519865621899</v>
+        <v>6.005219781635586</v>
       </c>
       <c r="D12" t="n">
-        <v>36.80245306257493</v>
+        <v>5.980398622668425</v>
       </c>
       <c r="E12" t="n">
-        <v>12.62548052830468</v>
+        <v>2.051640585849511</v>
       </c>
       <c r="F12" t="n">
-        <v>12.58098346174265</v>
+        <v>2.04440981253318</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>30.45290471696147</v>
+        <v>4.948597016506239</v>
       </c>
       <c r="D13" t="n">
-        <v>30.35626026045188</v>
+        <v>4.93289229232343</v>
       </c>
       <c r="E13" t="n">
-        <v>12.62548052830468</v>
+        <v>2.051640585849511</v>
       </c>
       <c r="F13" t="n">
-        <v>12.58098346174265</v>
+        <v>2.04440981253318</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>13.89091503371014</v>
+        <v>2.257273692977897</v>
       </c>
       <c r="D14" t="n">
-        <v>13.76215819350707</v>
+        <v>2.236350706444899</v>
       </c>
       <c r="E14" t="n">
-        <v>12.62548052830468</v>
+        <v>2.051640585849511</v>
       </c>
       <c r="F14" t="n">
-        <v>12.58098346174265</v>
+        <v>2.04440981253318</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>21.35889477507256</v>
+        <v>3.470820400949291</v>
       </c>
       <c r="D15" t="n">
-        <v>21.48196134042862</v>
+        <v>3.49081871781965</v>
       </c>
       <c r="E15" t="n">
-        <v>12.62548052830468</v>
+        <v>2.051640585849511</v>
       </c>
       <c r="F15" t="n">
-        <v>12.58098346174265</v>
+        <v>2.04440981253318</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>46.2429050390719</v>
+        <v>7.514472068849184</v>
       </c>
       <c r="D16" t="n">
-        <v>46.11444304361779</v>
+        <v>7.493596994587891</v>
       </c>
       <c r="E16" t="n">
-        <v>12.62548052830468</v>
+        <v>2.051640585849511</v>
       </c>
       <c r="F16" t="n">
-        <v>12.58098346174265</v>
+        <v>2.04440981253318</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>5.143477031307681</v>
+        <v>0.8358150175874981</v>
       </c>
       <c r="D17" t="n">
-        <v>5.504958744709544</v>
+        <v>0.8945557960153009</v>
       </c>
       <c r="E17" t="n">
-        <v>12.62548052830468</v>
+        <v>2.051640585849511</v>
       </c>
       <c r="F17" t="n">
-        <v>12.58098346174265</v>
+        <v>2.04440981253318</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>27.34247477281484</v>
+        <v>4.443152150582411</v>
       </c>
       <c r="D18" t="n">
-        <v>27.32498201118539</v>
+        <v>4.440309576817626</v>
       </c>
       <c r="E18" t="n">
-        <v>12.62548052830468</v>
+        <v>2.051640585849511</v>
       </c>
       <c r="F18" t="n">
-        <v>12.58098346174265</v>
+        <v>2.04440981253318</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
